--- a/Customer Database.xlsx
+++ b/Customer Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ps-fbzznf3\Lab\Lab recovery\Recreational Water\Final Reports\BacReportWebsite\BacteriologicalReports.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95D8FA3-9E5E-409D-AC7D-3EF950D84EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F993D65F-CCE0-4AD6-8897-475CF3E5C3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="3441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3777" uniqueCount="3450">
   <si>
     <t>2706</t>
   </si>
@@ -8963,9 +8963,6 @@
     <t>Winchester Apts       |Pool</t>
   </si>
   <si>
-    <t>C-CO235</t>
-  </si>
-  <si>
     <t>119</t>
   </si>
   <si>
@@ -10359,6 +10356,36 @@
   </si>
   <si>
     <t>T-HI180</t>
+  </si>
+  <si>
+    <t>C-WY104</t>
+  </si>
+  <si>
+    <t>C-WY102</t>
+  </si>
+  <si>
+    <t>YMCA-Beaver</t>
+  </si>
+  <si>
+    <t>YMCA-Beaver|Pool</t>
+  </si>
+  <si>
+    <t>YMCA-Beaver|Therapy</t>
+  </si>
+  <si>
+    <t>YMCA-Beaver|Spa</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>C-YM145</t>
   </si>
 </sst>
 </file>
@@ -10770,7 +10797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1456"/>
+  <dimension ref="A1:P1460"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -10793,18 +10820,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10903,7 +10930,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10995,7 +11022,7 @@
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>44</v>
@@ -11039,7 +11066,7 @@
     </row>
     <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>55</v>
@@ -11109,7 +11136,7 @@
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>71</v>
@@ -11211,7 +11238,7 @@
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>93</v>
@@ -11241,7 +11268,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -11471,7 +11498,7 @@
     </row>
     <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>155</v>
@@ -11509,7 +11536,7 @@
     </row>
     <row r="77" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>164</v>
@@ -11731,7 +11758,7 @@
         <v>218</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11742,7 +11769,7 @@
         <v>220</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -11823,7 +11850,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B111" t="s">
         <v>241</v>
@@ -11911,7 +11938,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B119" t="s">
         <v>262</v>
@@ -11933,7 +11960,7 @@
     </row>
     <row r="121" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>267</v>
@@ -12063,7 +12090,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="B135" t="s">
         <v>295</v>
@@ -12141,10 +12168,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B144" t="s">
         <v>3225</v>
-      </c>
-      <c r="B144" t="s">
-        <v>3226</v>
       </c>
     </row>
     <row r="145" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12187,7 +12214,7 @@
     </row>
     <row r="149" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>322</v>
@@ -12445,7 +12472,7 @@
     </row>
     <row r="173" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>389</v>
@@ -12707,7 +12734,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="B199" t="s">
         <v>456</v>
@@ -13069,7 +13096,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B239" t="s">
         <v>536</v>
@@ -13107,7 +13134,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="B243" t="s">
         <v>566</v>
@@ -13145,7 +13172,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="B247" t="s">
         <v>548</v>
@@ -13215,7 +13242,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="B255" t="s">
         <v>550</v>
@@ -13226,12 +13253,12 @@
         <v>2130</v>
       </c>
       <c r="B256" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="257" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>573</v>
@@ -13242,7 +13269,7 @@
         <v>570</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -13258,7 +13285,7 @@
         <v>574</v>
       </c>
       <c r="B260" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="261" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13291,7 +13318,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="B263" t="s">
         <v>578</v>
@@ -13465,7 +13492,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="B281" t="s">
         <v>617</v>
@@ -13609,10 +13636,10 @@
     </row>
     <row r="296" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>3227</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>3228</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -13829,7 +13856,7 @@
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>703</v>
@@ -13837,7 +13864,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B323" t="s">
         <v>704</v>
@@ -14293,7 +14320,7 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="B371" t="s">
         <v>813</v>
@@ -14331,7 +14358,7 @@
         <v>821</v>
       </c>
       <c r="C375" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -14433,7 +14460,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B387" t="s">
         <v>837</v>
@@ -14519,7 +14546,7 @@
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>861</v>
@@ -14575,15 +14602,15 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B404" t="s">
         <v>3229</v>
-      </c>
-      <c r="B404" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>873</v>
@@ -14723,7 +14750,7 @@
     </row>
     <row r="421" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>901</v>
@@ -15210,7 +15237,7 @@
         <v>1022</v>
       </c>
       <c r="B471" s="10" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -15239,7 +15266,7 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="B475" t="s">
         <v>1029</v>
@@ -15319,7 +15346,7 @@
     </row>
     <row r="485" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>1050</v>
@@ -15391,7 +15418,7 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B491" t="s">
         <v>1063</v>
@@ -15413,7 +15440,7 @@
     </row>
     <row r="493" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>1068</v>
@@ -16129,7 +16156,7 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B575" t="s">
         <v>1239</v>
@@ -16369,7 +16396,7 @@
     </row>
     <row r="599" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>1283</v>
@@ -16733,7 +16760,7 @@
     </row>
     <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>1368</v>
@@ -16879,7 +16906,7 @@
     </row>
     <row r="659" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>1403</v>
@@ -16955,7 +16982,7 @@
     </row>
     <row r="667" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>1423</v>
@@ -17169,7 +17196,7 @@
     </row>
     <row r="687" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>1473</v>
@@ -17202,13 +17229,13 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
+        <v>3376</v>
+      </c>
+      <c r="B690" t="s">
         <v>3377</v>
       </c>
-      <c r="B690" t="s">
+      <c r="C690" t="s">
         <v>3378</v>
-      </c>
-      <c r="C690" t="s">
-        <v>3379</v>
       </c>
     </row>
     <row r="691" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17273,7 +17300,7 @@
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B697" t="s">
         <v>1497</v>
@@ -17310,10 +17337,10 @@
         <v>1506</v>
       </c>
       <c r="F699" s="11" t="s">
+        <v>3437</v>
+      </c>
+      <c r="G699" s="11" t="s">
         <v>3438</v>
-      </c>
-      <c r="G699" s="11" t="s">
-        <v>3439</v>
       </c>
     </row>
     <row r="700" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17333,10 +17360,10 @@
         <v>1511</v>
       </c>
       <c r="F700" s="2" t="s">
+        <v>3435</v>
+      </c>
+      <c r="G700" s="2" t="s">
         <v>3436</v>
-      </c>
-      <c r="G700" s="2" t="s">
-        <v>3437</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.25">
@@ -17521,7 +17548,7 @@
     </row>
     <row r="719" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>1558</v>
@@ -17543,7 +17570,7 @@
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B721" t="s">
         <v>1563</v>
@@ -17565,7 +17592,7 @@
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>1568</v>
@@ -17587,7 +17614,7 @@
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B725" t="s">
         <v>1573</v>
@@ -17609,7 +17636,7 @@
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>1575</v>
@@ -17685,7 +17712,7 @@
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>1595</v>
@@ -17829,7 +17856,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B750" t="s">
         <v>1623</v>
@@ -17953,7 +17980,7 @@
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B761" t="s">
         <v>1657</v>
@@ -18005,7 +18032,7 @@
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="B766" t="s">
         <v>1669</v>
@@ -18115,7 +18142,7 @@
     </row>
     <row r="779" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>1696</v>
@@ -18137,7 +18164,7 @@
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="B781" t="s">
         <v>1701</v>
@@ -18171,7 +18198,7 @@
     </row>
     <row r="783" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>1705</v>
@@ -18247,7 +18274,7 @@
     </row>
     <row r="791" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="B791" s="2" t="s">
         <v>1729</v>
@@ -18420,13 +18447,13 @@
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B810" t="s">
         <v>3300</v>
       </c>
-      <c r="B810" t="s">
+      <c r="C810" t="s">
         <v>3301</v>
-      </c>
-      <c r="C810" t="s">
-        <v>3302</v>
       </c>
     </row>
     <row r="811" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18541,7 +18568,7 @@
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B821" t="s">
         <v>1801</v>
@@ -18723,15 +18750,15 @@
     </row>
     <row r="840" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B840" s="2" t="s">
         <v>3231</v>
-      </c>
-      <c r="B840" s="2" t="s">
-        <v>3232</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="B841" t="s">
         <v>1846</v>
@@ -18755,10 +18782,10 @@
     </row>
     <row r="844" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B844" s="2" t="s">
         <v>3233</v>
-      </c>
-      <c r="B844" s="2" t="s">
-        <v>3234</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.25">
@@ -19033,7 +19060,7 @@
     </row>
     <row r="875" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B875" t="s">
         <v>1913</v>
@@ -19071,7 +19098,7 @@
     </row>
     <row r="879" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B879" t="s">
         <v>1922</v>
@@ -19093,7 +19120,7 @@
     </row>
     <row r="881" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>1927</v>
@@ -19187,7 +19214,7 @@
     </row>
     <row r="889" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>1952</v>
@@ -19315,10 +19342,10 @@
         <v>1981</v>
       </c>
       <c r="C899" s="10" t="s">
+        <v>3396</v>
+      </c>
+      <c r="D899" s="10" t="s">
         <v>3397</v>
-      </c>
-      <c r="D899" s="10" t="s">
-        <v>3398</v>
       </c>
     </row>
     <row r="900" spans="1:4" x14ac:dyDescent="0.25">
@@ -19326,13 +19353,13 @@
         <v>1982</v>
       </c>
       <c r="B900" t="s">
+        <v>3398</v>
+      </c>
+      <c r="C900" t="s">
         <v>3399</v>
       </c>
-      <c r="C900" t="s">
+      <c r="D900" t="s">
         <v>3400</v>
-      </c>
-      <c r="D900" t="s">
-        <v>3401</v>
       </c>
     </row>
     <row r="901" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19537,7 +19564,7 @@
     </row>
     <row r="923" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B923" t="s">
         <v>2031</v>
@@ -19609,7 +19636,7 @@
     </row>
     <row r="929" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B929" s="2" t="s">
         <v>2050</v>
@@ -19841,10 +19868,10 @@
     </row>
     <row r="952" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B952" t="s">
         <v>3348</v>
-      </c>
-      <c r="B952" t="s">
-        <v>3349</v>
       </c>
     </row>
     <row r="953" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19957,7 +19984,7 @@
     </row>
     <row r="965" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B965" s="2" t="s">
         <v>2136</v>
@@ -20255,7 +20282,7 @@
     </row>
     <row r="997" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B997" s="2" t="s">
         <v>2205</v>
@@ -20354,7 +20381,7 @@
         <v>2232</v>
       </c>
       <c r="C1006" s="2" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="1007" spans="1:3" x14ac:dyDescent="0.25">
@@ -20491,52 +20518,52 @@
     </row>
     <row r="1016" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1016" t="s">
         <v>3303</v>
       </c>
-      <c r="B1016" t="s">
+      <c r="C1016" t="s">
         <v>3304</v>
       </c>
-      <c r="C1016" t="s">
+      <c r="D1016" t="s">
         <v>3305</v>
       </c>
-      <c r="D1016" t="s">
+      <c r="E1016" t="s">
         <v>3306</v>
       </c>
-      <c r="E1016" t="s">
+      <c r="F1016" t="s">
         <v>3307</v>
       </c>
-      <c r="F1016" t="s">
+      <c r="G1016" t="s">
         <v>3308</v>
       </c>
-      <c r="G1016" t="s">
+      <c r="H1016" t="s">
         <v>3309</v>
       </c>
-      <c r="H1016" t="s">
+      <c r="I1016" t="s">
         <v>3310</v>
       </c>
-      <c r="I1016" t="s">
+      <c r="J1016" t="s">
+        <v>3310</v>
+      </c>
+      <c r="K1016" t="s">
         <v>3311</v>
       </c>
-      <c r="J1016" t="s">
-        <v>3311</v>
-      </c>
-      <c r="K1016" t="s">
+      <c r="L1016" t="s">
         <v>3312</v>
       </c>
-      <c r="L1016" t="s">
+      <c r="M1016" t="s">
         <v>3313</v>
       </c>
-      <c r="M1016" t="s">
+      <c r="N1016" t="s">
         <v>3314</v>
       </c>
-      <c r="N1016" t="s">
+      <c r="O1016" t="s">
         <v>3315</v>
       </c>
-      <c r="O1016" t="s">
+      <c r="P1016" t="s">
         <v>3316</v>
-      </c>
-      <c r="P1016" t="s">
-        <v>3317</v>
       </c>
     </row>
     <row r="1017" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20557,7 +20584,7 @@
     </row>
     <row r="1019" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1019" t="s">
         <v>2270</v>
@@ -20579,7 +20606,7 @@
     </row>
     <row r="1021" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B1021" s="2" t="s">
         <v>2275</v>
@@ -20648,10 +20675,10 @@
         <v>2292</v>
       </c>
       <c r="B1027" s="10" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C1027" s="10" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
@@ -20747,7 +20774,7 @@
         <v>2318</v>
       </c>
       <c r="I1033" s="11" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="1034" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -20773,7 +20800,7 @@
         <v>2325</v>
       </c>
       <c r="H1034" s="2" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="I1034" s="2" t="s">
         <v>2326</v>
@@ -20935,7 +20962,7 @@
     </row>
     <row r="1049" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1049" s="2" t="s">
         <v>2367</v>
@@ -21395,7 +21422,7 @@
     </row>
     <row r="1099" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1099" s="2" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="B1099" s="2" t="s">
         <v>2479</v>
@@ -21525,7 +21552,7 @@
     </row>
     <row r="1113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1113" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1113" s="2" t="s">
         <v>2511</v>
@@ -22053,16 +22080,16 @@
     </row>
     <row r="1170" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1170" s="2" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B1170" s="2" t="s">
         <v>3318</v>
       </c>
-      <c r="B1170" s="2" t="s">
+      <c r="C1170" s="2" t="s">
         <v>3319</v>
       </c>
-      <c r="C1170" s="2" t="s">
+      <c r="D1170" s="2" t="s">
         <v>3320</v>
-      </c>
-      <c r="D1170" s="2" t="s">
-        <v>3321</v>
       </c>
     </row>
     <row r="1171" spans="1:4" x14ac:dyDescent="0.25">
@@ -22089,7 +22116,7 @@
     </row>
     <row r="1173" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="2" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B1173" s="2" t="s">
         <v>2637</v>
@@ -22253,7 +22280,7 @@
     </row>
     <row r="1189" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1189" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B1189" s="2" t="s">
         <v>2670</v>
@@ -22519,7 +22546,7 @@
     </row>
     <row r="1211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="B1211" t="s">
         <v>2749</v>
@@ -22575,7 +22602,7 @@
     </row>
     <row r="1218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="B1218" t="s">
         <v>2761</v>
@@ -22755,7 +22782,7 @@
     </row>
     <row r="1239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1239" s="2" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B1239" s="2" t="s">
         <v>2803</v>
@@ -23003,7 +23030,7 @@
     </row>
     <row r="1267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1267" s="2" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="B1267" s="2" t="s">
         <v>2856</v>
@@ -23051,7 +23078,7 @@
     </row>
     <row r="1273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B1273" t="s">
         <v>2866</v>
@@ -23117,7 +23144,7 @@
     </row>
     <row r="1279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1279" s="2" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1279" s="2" t="s">
         <v>2883</v>
@@ -23155,7 +23182,7 @@
     </row>
     <row r="1283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1283" s="2" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B1283" s="2" t="s">
         <v>2895</v>
@@ -23215,7 +23242,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1289" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1289" t="s">
         <v>2909</v>
@@ -23277,10 +23304,10 @@
     </row>
     <row r="1296" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1296" s="2" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B1296" s="2" t="s">
         <v>3296</v>
-      </c>
-      <c r="B1296" s="2" t="s">
-        <v>3297</v>
       </c>
     </row>
     <row r="1297" spans="1:4" x14ac:dyDescent="0.25">
@@ -23413,7 +23440,7 @@
     </row>
     <row r="1307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B1307" t="s">
         <v>2960</v>
@@ -23473,232 +23500,226 @@
     </row>
     <row r="1313" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1313" s="2" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B1313" s="2" t="s">
         <v>2975</v>
       </c>
-      <c r="B1313" s="2" t="s">
+      <c r="C1313" s="2" t="s">
         <v>2976</v>
-      </c>
-      <c r="C1313" s="2" t="s">
-        <v>2977</v>
-      </c>
-      <c r="D1313" s="2" t="s">
-        <v>2978</v>
       </c>
     </row>
     <row r="1314" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="2" t="s">
+        <v>2978</v>
+      </c>
+      <c r="B1314" s="2" t="s">
         <v>2979</v>
       </c>
-      <c r="B1314" s="2" t="s">
-        <v>2980</v>
-      </c>
       <c r="C1314" s="2" t="s">
-        <v>2981</v>
-      </c>
-      <c r="D1314" s="2" t="s">
         <v>2980</v>
       </c>
     </row>
     <row r="1315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
+        <v>2981</v>
+      </c>
+      <c r="B1315" t="s">
         <v>2982</v>
-      </c>
-      <c r="B1315" t="s">
-        <v>2983</v>
       </c>
     </row>
     <row r="1316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1316" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B1316" t="s">
         <v>2985</v>
-      </c>
-      <c r="B1316" t="s">
-        <v>2986</v>
       </c>
     </row>
     <row r="1317" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1317" s="2" t="s">
+        <v>2987</v>
+      </c>
+      <c r="B1317" s="2" t="s">
         <v>2988</v>
       </c>
-      <c r="B1317" s="2" t="s">
+      <c r="C1317" s="2" t="s">
         <v>2989</v>
       </c>
-      <c r="C1317" s="2" t="s">
+      <c r="D1317" s="2" t="s">
         <v>2990</v>
-      </c>
-      <c r="D1317" s="2" t="s">
-        <v>2991</v>
       </c>
     </row>
     <row r="1318" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1318" s="2" t="s">
+        <v>2991</v>
+      </c>
+      <c r="B1318" s="2" t="s">
         <v>2992</v>
       </c>
-      <c r="B1318" s="2" t="s">
+      <c r="C1318" s="2" t="s">
         <v>2993</v>
       </c>
-      <c r="C1318" s="2" t="s">
+      <c r="D1318" s="2" t="s">
         <v>2994</v>
-      </c>
-      <c r="D1318" s="2" t="s">
-        <v>2995</v>
       </c>
     </row>
     <row r="1319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
+        <v>2995</v>
+      </c>
+      <c r="B1319" t="s">
         <v>2996</v>
       </c>
-      <c r="B1319" t="s">
+      <c r="C1319" t="s">
         <v>2997</v>
-      </c>
-      <c r="C1319" t="s">
-        <v>2998</v>
       </c>
     </row>
     <row r="1320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
+        <v>2998</v>
+      </c>
+      <c r="B1320" t="s">
         <v>2999</v>
       </c>
-      <c r="B1320" t="s">
+      <c r="C1320" t="s">
         <v>3000</v>
-      </c>
-      <c r="C1320" t="s">
-        <v>3001</v>
       </c>
     </row>
     <row r="1321" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1321" s="2" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="1322" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1322" s="2" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B1322" s="2" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="1323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B1323" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="1324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1324" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B1324" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="1325" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1325" s="2" t="s">
+        <v>3007</v>
+      </c>
+      <c r="B1325" s="2" t="s">
         <v>3008</v>
       </c>
-      <c r="B1325" s="2" t="s">
+      <c r="C1325" s="2" t="s">
         <v>3009</v>
-      </c>
-      <c r="C1325" s="2" t="s">
-        <v>3010</v>
       </c>
     </row>
     <row r="1326" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1326" s="2" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B1326" s="2" t="s">
         <v>3011</v>
       </c>
-      <c r="B1326" s="2" t="s">
+      <c r="C1326" s="2" t="s">
         <v>3012</v>
-      </c>
-      <c r="C1326" s="2" t="s">
-        <v>3013</v>
       </c>
     </row>
     <row r="1327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1327" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B1327" t="s">
         <v>3014</v>
-      </c>
-      <c r="B1327" t="s">
-        <v>3015</v>
       </c>
     </row>
     <row r="1328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1328" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B1328" t="s">
         <v>3016</v>
-      </c>
-      <c r="B1328" t="s">
-        <v>3017</v>
       </c>
     </row>
     <row r="1329" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1329" s="2" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="1330" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1330" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1331" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B1331" t="s">
         <v>3020</v>
       </c>
-      <c r="B1331" t="s">
+      <c r="C1331" t="s">
         <v>3021</v>
-      </c>
-      <c r="C1331" t="s">
-        <v>3022</v>
       </c>
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1332" t="s">
+        <v>3023</v>
+      </c>
+      <c r="B1332" t="s">
         <v>3024</v>
       </c>
-      <c r="B1332" t="s">
+      <c r="C1332" t="s">
         <v>3025</v>
-      </c>
-      <c r="C1332" t="s">
-        <v>3026</v>
       </c>
     </row>
     <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B1333" t="s">
         <v>3028</v>
       </c>
-      <c r="B1333" t="s">
+      <c r="C1333" t="s">
         <v>3029</v>
       </c>
-      <c r="C1333" t="s">
+      <c r="D1333" t="s">
         <v>3030</v>
-      </c>
-      <c r="D1333" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B1334" t="s">
         <v>3032</v>
       </c>
-      <c r="B1334" t="s">
+      <c r="C1334" t="s">
         <v>3033</v>
       </c>
-      <c r="C1334" t="s">
+      <c r="D1334" t="s">
         <v>3034</v>
-      </c>
-      <c r="D1334" t="s">
-        <v>3035</v>
       </c>
     </row>
     <row r="1335" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -23706,343 +23727,343 @@
         <v>7</v>
       </c>
       <c r="B1335" s="2" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C1335" s="2" t="s">
         <v>3036</v>
-      </c>
-      <c r="C1335" s="2" t="s">
-        <v>3037</v>
       </c>
     </row>
     <row r="1336" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1336" s="2" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B1336" s="2" t="s">
         <v>3038</v>
       </c>
-      <c r="B1336" s="2" t="s">
+      <c r="C1336" s="2" t="s">
         <v>3039</v>
-      </c>
-      <c r="C1336" s="2" t="s">
-        <v>3040</v>
       </c>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B1337" t="s">
         <v>3041</v>
-      </c>
-      <c r="B1337" t="s">
-        <v>3042</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1338" t="s">
+        <v>3042</v>
+      </c>
+      <c r="B1338" t="s">
         <v>3043</v>
-      </c>
-      <c r="B1338" t="s">
-        <v>3044</v>
       </c>
     </row>
     <row r="1339" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1339" s="2" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1339" s="2" t="s">
         <v>3045</v>
       </c>
-      <c r="B1339" s="2" t="s">
+      <c r="C1339" s="2" t="s">
         <v>3046</v>
-      </c>
-      <c r="C1339" s="2" t="s">
-        <v>3047</v>
       </c>
     </row>
     <row r="1340" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1340" s="2" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B1340" s="2" t="s">
         <v>3048</v>
       </c>
-      <c r="B1340" s="2" t="s">
+      <c r="C1340" s="2" t="s">
         <v>3049</v>
-      </c>
-      <c r="C1340" s="2" t="s">
-        <v>3050</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B1341" t="s">
         <v>3051</v>
       </c>
-      <c r="B1341" t="s">
+      <c r="C1341" t="s">
         <v>3052</v>
       </c>
-      <c r="C1341" t="s">
+      <c r="D1341" t="s">
         <v>3053</v>
-      </c>
-      <c r="D1341" t="s">
-        <v>3054</v>
       </c>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B1342" t="s">
         <v>3055</v>
       </c>
-      <c r="B1342" t="s">
+      <c r="C1342" t="s">
         <v>3056</v>
       </c>
-      <c r="C1342" t="s">
+      <c r="D1342" t="s">
         <v>3057</v>
-      </c>
-      <c r="D1342" t="s">
-        <v>3058</v>
       </c>
     </row>
     <row r="1343" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1343" s="2" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B1343" s="2" t="s">
         <v>3059</v>
       </c>
-      <c r="B1343" s="2" t="s">
+      <c r="C1343" s="2" t="s">
         <v>3060</v>
       </c>
-      <c r="C1343" s="2" t="s">
+      <c r="D1343" s="2" t="s">
         <v>3061</v>
       </c>
-      <c r="D1343" s="2" t="s">
+      <c r="E1343" s="2" t="s">
         <v>3062</v>
       </c>
-      <c r="E1343" s="2" t="s">
+      <c r="F1343" s="2" t="s">
         <v>3063</v>
       </c>
-      <c r="F1343" s="2" t="s">
+      <c r="G1343" s="2" t="s">
         <v>3064</v>
-      </c>
-      <c r="G1343" s="2" t="s">
-        <v>3065</v>
       </c>
     </row>
     <row r="1344" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1344" s="2" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B1344" s="2" t="s">
         <v>3066</v>
       </c>
-      <c r="B1344" s="2" t="s">
+      <c r="C1344" s="2" t="s">
         <v>3067</v>
       </c>
-      <c r="C1344" s="2" t="s">
+      <c r="D1344" s="2" t="s">
         <v>3068</v>
       </c>
-      <c r="D1344" s="2" t="s">
+      <c r="E1344" s="2" t="s">
+        <v>3066</v>
+      </c>
+      <c r="F1344" s="2" t="s">
         <v>3069</v>
       </c>
-      <c r="E1344" s="2" t="s">
-        <v>3067</v>
-      </c>
-      <c r="F1344" s="2" t="s">
+      <c r="G1344" s="2" t="s">
         <v>3070</v>
-      </c>
-      <c r="G1344" s="2" t="s">
-        <v>3071</v>
       </c>
     </row>
     <row r="1345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1345" t="s">
+        <v>3071</v>
+      </c>
+      <c r="B1345" t="s">
         <v>3072</v>
       </c>
-      <c r="B1345" t="s">
+      <c r="C1345" t="s">
         <v>3073</v>
       </c>
-      <c r="C1345" t="s">
+      <c r="D1345" t="s">
         <v>3074</v>
       </c>
-      <c r="D1345" t="s">
+      <c r="E1345" t="s">
         <v>3075</v>
-      </c>
-      <c r="E1345" t="s">
-        <v>3076</v>
       </c>
     </row>
     <row r="1346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1346" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B1346" t="s">
         <v>3077</v>
       </c>
-      <c r="B1346" t="s">
+      <c r="C1346" t="s">
         <v>3078</v>
       </c>
-      <c r="C1346" t="s">
+      <c r="D1346" t="s">
         <v>3079</v>
       </c>
-      <c r="D1346" t="s">
+      <c r="E1346" t="s">
         <v>3080</v>
-      </c>
-      <c r="E1346" t="s">
-        <v>3081</v>
       </c>
     </row>
     <row r="1347" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1347" s="2" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B1347" s="2" t="s">
         <v>3082</v>
-      </c>
-      <c r="B1347" s="2" t="s">
-        <v>3083</v>
       </c>
     </row>
     <row r="1348" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1348" s="2" t="s">
+        <v>3083</v>
+      </c>
+      <c r="B1348" s="2" t="s">
         <v>3084</v>
-      </c>
-      <c r="B1348" s="2" t="s">
-        <v>3085</v>
       </c>
     </row>
     <row r="1349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1349" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B1349" t="s">
         <v>3086</v>
       </c>
-      <c r="B1349" t="s">
+      <c r="C1349" t="s">
         <v>3087</v>
       </c>
-      <c r="C1349" t="s">
+      <c r="D1349" t="s">
         <v>3088</v>
       </c>
-      <c r="D1349" t="s">
+      <c r="E1349" t="s">
         <v>3089</v>
-      </c>
-      <c r="E1349" t="s">
-        <v>3090</v>
       </c>
     </row>
     <row r="1350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1350" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B1350" t="s">
         <v>3091</v>
       </c>
-      <c r="B1350" t="s">
+      <c r="C1350" t="s">
         <v>3092</v>
       </c>
-      <c r="C1350" t="s">
+      <c r="D1350" t="s">
         <v>3093</v>
       </c>
-      <c r="D1350" t="s">
+      <c r="E1350" t="s">
         <v>3094</v>
-      </c>
-      <c r="E1350" t="s">
-        <v>3095</v>
       </c>
     </row>
     <row r="1351" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1351" s="2" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B1351" s="2" t="s">
         <v>3096</v>
-      </c>
-      <c r="B1351" s="2" t="s">
-        <v>3097</v>
       </c>
     </row>
     <row r="1352" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1352" s="2" t="s">
+        <v>3097</v>
+      </c>
+      <c r="B1352" s="2" t="s">
         <v>3098</v>
-      </c>
-      <c r="B1352" s="2" t="s">
-        <v>3099</v>
       </c>
     </row>
     <row r="1353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1353" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B1353" t="s">
         <v>3100</v>
-      </c>
-      <c r="B1353" t="s">
-        <v>3101</v>
       </c>
     </row>
     <row r="1354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1354" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B1354" t="s">
         <v>3104</v>
-      </c>
-      <c r="B1354" t="s">
-        <v>3105</v>
       </c>
     </row>
     <row r="1355" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1355" s="2" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B1355" s="2" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C1355" s="2" t="s">
         <v>3102</v>
-      </c>
-      <c r="C1355" s="2" t="s">
-        <v>3103</v>
       </c>
     </row>
     <row r="1356" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1356" s="2" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="B1356" s="2" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1356" s="2" t="s">
         <v>3106</v>
-      </c>
-      <c r="C1356" s="2" t="s">
-        <v>3107</v>
       </c>
     </row>
     <row r="1357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1357" t="s">
+        <v>3109</v>
+      </c>
+      <c r="B1357" t="s">
         <v>3110</v>
       </c>
-      <c r="B1357" t="s">
+      <c r="C1357" t="s">
         <v>3111</v>
-      </c>
-      <c r="C1357" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="1358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B1358" t="s">
         <v>3113</v>
       </c>
-      <c r="B1358" t="s">
+      <c r="C1358" t="s">
         <v>3114</v>
-      </c>
-      <c r="C1358" t="s">
-        <v>3115</v>
       </c>
     </row>
     <row r="1359" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="2" t="s">
+        <v>3115</v>
+      </c>
+      <c r="B1359" s="2" t="s">
         <v>3116</v>
       </c>
-      <c r="B1359" s="2" t="s">
+      <c r="C1359" s="2" t="s">
         <v>3117</v>
       </c>
-      <c r="C1359" s="2" t="s">
+      <c r="D1359" s="2" t="s">
         <v>3118</v>
-      </c>
-      <c r="D1359" s="2" t="s">
-        <v>3119</v>
       </c>
     </row>
     <row r="1360" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="2" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B1360" s="2" t="s">
         <v>3122</v>
       </c>
-      <c r="B1360" s="2" t="s">
+      <c r="C1360" s="2" t="s">
         <v>3123</v>
       </c>
-      <c r="C1360" s="2" t="s">
+      <c r="D1360" s="2" t="s">
         <v>3124</v>
-      </c>
-      <c r="D1360" s="2" t="s">
-        <v>3125</v>
       </c>
     </row>
     <row r="1361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="B1361" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C1361" t="s">
         <v>3120</v>
-      </c>
-      <c r="C1361" t="s">
-        <v>3121</v>
       </c>
     </row>
     <row r="1362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="B1362" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1362" t="s">
         <v>3126</v>
-      </c>
-      <c r="C1362" t="s">
-        <v>3127</v>
       </c>
     </row>
     <row r="1363" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24050,165 +24071,165 @@
         <v>7</v>
       </c>
       <c r="B1363" s="8" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="1364" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1364" s="4" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1364" s="4" t="s">
         <v>3153</v>
-      </c>
-      <c r="B1364" s="4" t="s">
-        <v>3154</v>
       </c>
     </row>
     <row r="1365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1365" s="6" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="B1365" s="9" t="s">
+        <v>3245</v>
+      </c>
+      <c r="C1365" s="9" t="s">
         <v>3246</v>
-      </c>
-      <c r="C1365" s="9" t="s">
-        <v>3247</v>
       </c>
     </row>
     <row r="1366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1366" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B1366" t="s">
         <v>3156</v>
       </c>
-      <c r="B1366" t="s">
+      <c r="C1366" t="s">
         <v>3157</v>
-      </c>
-      <c r="C1366" t="s">
-        <v>3158</v>
       </c>
     </row>
     <row r="1367" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1367" s="4" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="B1367" s="8" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C1367" s="8" t="s">
         <v>3248</v>
       </c>
-      <c r="C1367" s="8" t="s">
+      <c r="D1367" s="8" t="s">
         <v>3249</v>
-      </c>
-      <c r="D1367" s="8" t="s">
-        <v>3250</v>
       </c>
     </row>
     <row r="1368" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1368" s="4" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B1368" s="4" t="s">
         <v>3160</v>
       </c>
-      <c r="B1368" s="4" t="s">
+      <c r="C1368" s="4" t="s">
         <v>3161</v>
       </c>
-      <c r="C1368" s="4" t="s">
+      <c r="D1368" s="4" t="s">
         <v>3162</v>
-      </c>
-      <c r="D1368" s="4" t="s">
-        <v>3163</v>
       </c>
     </row>
     <row r="1369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1369" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B1369" s="9" t="s">
+        <v>3250</v>
+      </c>
+      <c r="C1369" s="9" t="s">
         <v>3251</v>
       </c>
-      <c r="C1369" s="9" t="s">
+      <c r="D1369" s="9" t="s">
         <v>3252</v>
-      </c>
-      <c r="D1369" s="9" t="s">
-        <v>3253</v>
       </c>
     </row>
     <row r="1370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1370" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1370" t="s">
         <v>3165</v>
       </c>
-      <c r="B1370" t="s">
+      <c r="C1370" t="s">
         <v>3166</v>
       </c>
-      <c r="C1370" t="s">
+      <c r="D1370" t="s">
         <v>3167</v>
-      </c>
-      <c r="D1370" t="s">
-        <v>3168</v>
       </c>
     </row>
     <row r="1371" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1371" s="4" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="B1371" s="8" t="s">
+        <v>3253</v>
+      </c>
+      <c r="C1371" s="8" t="s">
         <v>3254</v>
       </c>
-      <c r="C1371" s="8" t="s">
+      <c r="D1371" s="8" t="s">
         <v>3255</v>
-      </c>
-      <c r="D1371" s="8" t="s">
-        <v>3256</v>
       </c>
     </row>
     <row r="1372" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1372" s="4" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B1372" s="4" t="s">
         <v>3170</v>
       </c>
-      <c r="B1372" s="4" t="s">
+      <c r="C1372" s="4" t="s">
         <v>3171</v>
       </c>
-      <c r="C1372" s="4" t="s">
+      <c r="D1372" s="4" t="s">
         <v>3172</v>
-      </c>
-      <c r="D1372" s="4" t="s">
-        <v>3173</v>
       </c>
     </row>
     <row r="1373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1373" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B1373" s="9" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="1374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1374" t="s">
+        <v>3173</v>
+      </c>
+      <c r="B1374" t="s">
         <v>3174</v>
-      </c>
-      <c r="B1374" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="1375" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="4" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="B1375" s="8" t="s">
+        <v>3257</v>
+      </c>
+      <c r="C1375" s="8" t="s">
         <v>3258</v>
       </c>
-      <c r="C1375" s="8" t="s">
+      <c r="D1375" s="8" t="s">
         <v>3259</v>
-      </c>
-      <c r="D1375" s="8" t="s">
-        <v>3260</v>
       </c>
     </row>
     <row r="1376" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1376" s="4" t="s">
+        <v>3176</v>
+      </c>
+      <c r="B1376" s="4" t="s">
         <v>3177</v>
       </c>
-      <c r="B1376" s="4" t="s">
+      <c r="C1376" s="4" t="s">
         <v>3178</v>
       </c>
-      <c r="C1376" s="4" t="s">
+      <c r="D1376" s="4" t="s">
         <v>3179</v>
-      </c>
-      <c r="D1376" s="4" t="s">
-        <v>3180</v>
       </c>
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.25">
@@ -24216,60 +24237,60 @@
         <v>199</v>
       </c>
       <c r="B1377" s="9" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="1378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1378" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B1378" t="s">
         <v>3181</v>
-      </c>
-      <c r="B1378" t="s">
-        <v>3182</v>
       </c>
     </row>
     <row r="1379" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1379" s="4" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1379" s="8" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="1380" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="4" t="s">
+        <v>3183</v>
+      </c>
+      <c r="B1380" s="4" t="s">
         <v>3184</v>
-      </c>
-      <c r="B1380" s="4" t="s">
-        <v>3185</v>
       </c>
     </row>
     <row r="1381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1381" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="B1381" s="9" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="1382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1382" t="s">
+        <v>3185</v>
+      </c>
+      <c r="B1382" t="s">
         <v>3186</v>
-      </c>
-      <c r="B1382" t="s">
-        <v>3187</v>
       </c>
     </row>
     <row r="1383" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1383" s="4" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="B1383" s="8" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="1384" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1384" s="7" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B1384" s="4" t="s">
         <v>547</v>
@@ -24277,79 +24298,79 @@
     </row>
     <row r="1385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1385" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="B1385" s="9" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C1385" s="9" t="s">
         <v>3265</v>
-      </c>
-      <c r="C1385" s="9" t="s">
-        <v>3266</v>
       </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1386" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B1386" t="s">
         <v>3192</v>
       </c>
-      <c r="B1386" t="s">
+      <c r="C1386" t="s">
         <v>3193</v>
-      </c>
-      <c r="C1386" t="s">
-        <v>3194</v>
       </c>
     </row>
     <row r="1387" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1387" s="4" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B1387" s="8" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C1387" s="8" t="s">
         <v>3241</v>
-      </c>
-      <c r="C1387" s="8" t="s">
-        <v>3242</v>
       </c>
     </row>
     <row r="1388" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1388" s="4" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B1388" s="4" t="s">
+        <v>3192</v>
+      </c>
+      <c r="C1388" s="4" t="s">
         <v>3193</v>
-      </c>
-      <c r="C1388" s="4" t="s">
-        <v>3194</v>
       </c>
     </row>
     <row r="1389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1389" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B1389" s="10" t="s">
         <v>3197</v>
-      </c>
-      <c r="B1389" s="10" t="s">
-        <v>3198</v>
       </c>
     </row>
     <row r="1390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1390" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B1390" s="5" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="C1390" s="5"/>
     </row>
     <row r="1391" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1391" s="4" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B1391" s="8" t="s">
+        <v>3204</v>
+      </c>
+      <c r="C1391" s="8" t="s">
         <v>3205</v>
-      </c>
-      <c r="C1391" s="8" t="s">
-        <v>3206</v>
       </c>
     </row>
     <row r="1392" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1392" s="4" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B1392" s="4" t="s">
         <v>1105</v>
@@ -24360,196 +24381,196 @@
     </row>
     <row r="1393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1393" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B1393" s="10" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
     </row>
     <row r="1394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1394" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B1394" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="1395" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1395" s="4" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="B1395" s="8" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="C1395" s="8" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="1396" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1396" s="4" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B1396" s="4" t="s">
+        <v>3212</v>
+      </c>
+      <c r="C1396" s="4" t="s">
         <v>3213</v>
-      </c>
-      <c r="C1396" s="4" t="s">
-        <v>3214</v>
       </c>
     </row>
     <row r="1397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1397" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="B1397" s="10" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C1397" s="10" t="s">
         <v>3218</v>
       </c>
-      <c r="C1397" s="10" t="s">
+      <c r="D1397" s="10" t="s">
         <v>3219</v>
-      </c>
-      <c r="D1397" s="10" t="s">
-        <v>3220</v>
       </c>
     </row>
     <row r="1398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1398" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="B1398" t="s">
+        <v>3220</v>
+      </c>
+      <c r="C1398" t="s">
         <v>3221</v>
       </c>
-      <c r="C1398" t="s">
+      <c r="D1398" t="s">
         <v>3222</v>
-      </c>
-      <c r="D1398" t="s">
-        <v>3223</v>
       </c>
     </row>
     <row r="1399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1399" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="B1399" s="10" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="1400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1400" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B1400" t="s">
         <v>3353</v>
-      </c>
-      <c r="B1400" t="s">
-        <v>3354</v>
       </c>
     </row>
     <row r="1401" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1401" s="4" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="B1401" s="8" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="C1401" s="8"/>
     </row>
     <row r="1402" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1402" s="4" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B1402" s="4" t="s">
         <v>3238</v>
-      </c>
-      <c r="B1402" s="4" t="s">
-        <v>3239</v>
       </c>
     </row>
     <row r="1403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1403" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B1403" s="10" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C1403" s="10" t="s">
         <v>3286</v>
-      </c>
-      <c r="C1403" s="10" t="s">
-        <v>3287</v>
       </c>
     </row>
     <row r="1404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1404" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B1404" t="s">
+        <v>3283</v>
+      </c>
+      <c r="C1404" t="s">
         <v>3284</v>
-      </c>
-      <c r="C1404" t="s">
-        <v>3285</v>
       </c>
     </row>
     <row r="1405" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1405" s="4" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="B1405" s="8" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="C1405" s="8"/>
     </row>
     <row r="1406" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1406" s="4" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="B1406" s="4" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="1407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1407" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="B1407" s="10" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="1408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1408" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B1408" t="s">
         <v>3280</v>
-      </c>
-      <c r="B1408" t="s">
-        <v>3281</v>
       </c>
     </row>
     <row r="1409" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1409" s="4" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="B1409" s="8" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="C1409" s="8" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="D1409" s="4" t="s">
+        <v>3272</v>
+      </c>
+      <c r="E1409" s="4" t="s">
         <v>3273</v>
       </c>
-      <c r="E1409" s="4" t="s">
-        <v>3274</v>
-      </c>
       <c r="F1409" s="4" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="1410" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1410" s="4" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B1410" s="4" t="s">
         <v>3289</v>
       </c>
-      <c r="B1410" s="4" t="s">
+      <c r="C1410" s="4" t="s">
+        <v>3291</v>
+      </c>
+      <c r="D1410" s="4" t="s">
+        <v>3293</v>
+      </c>
+      <c r="E1410" s="4" t="s">
         <v>3290</v>
       </c>
-      <c r="C1410" s="4" t="s">
+      <c r="F1410" s="4" t="s">
         <v>3292</v>
-      </c>
-      <c r="D1410" s="4" t="s">
-        <v>3294</v>
-      </c>
-      <c r="E1410" s="4" t="s">
-        <v>3291</v>
-      </c>
-      <c r="F1410" s="4" t="s">
-        <v>3293</v>
       </c>
     </row>
     <row r="1411" spans="1:6" x14ac:dyDescent="0.25">
@@ -24557,32 +24578,32 @@
         <v>7</v>
       </c>
       <c r="B1411" s="10" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="1412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1412" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="B1412" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="1413" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1413" s="4" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="B1413" s="8" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="C1413" s="8"/>
     </row>
     <row r="1414" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1414" s="4" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="B1414" s="4" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="1415" spans="1:6" x14ac:dyDescent="0.25">
@@ -24590,21 +24611,21 @@
         <v>7</v>
       </c>
       <c r="B1415" s="10" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C1415" s="10" t="s">
         <v>3328</v>
-      </c>
-      <c r="C1415" s="10" t="s">
-        <v>3329</v>
       </c>
     </row>
     <row r="1416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1416" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="B1416" t="s">
+        <v>3329</v>
+      </c>
+      <c r="C1416" t="s">
         <v>3330</v>
-      </c>
-      <c r="C1416" t="s">
-        <v>3331</v>
       </c>
     </row>
     <row r="1417" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24612,16 +24633,16 @@
         <v>7</v>
       </c>
       <c r="B1417" s="8" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="C1417" s="8"/>
     </row>
     <row r="1418" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="4" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="B1418" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="1419" spans="1:6" x14ac:dyDescent="0.25">
@@ -24629,15 +24650,15 @@
         <v>199</v>
       </c>
       <c r="B1419" s="10" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="1420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1420" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B1420" t="s">
         <v>3335</v>
-      </c>
-      <c r="B1420" t="s">
-        <v>3336</v>
       </c>
     </row>
     <row r="1421" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24645,27 +24666,27 @@
         <v>199</v>
       </c>
       <c r="B1421" s="12" t="s">
+        <v>3342</v>
+      </c>
+      <c r="C1421" s="12" t="s">
         <v>3343</v>
       </c>
-      <c r="C1421" s="12" t="s">
+      <c r="D1421" s="12" t="s">
         <v>3344</v>
-      </c>
-      <c r="D1421" s="12" t="s">
-        <v>3345</v>
       </c>
     </row>
     <row r="1422" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1422" s="4" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="B1422" s="4" t="s">
+        <v>3339</v>
+      </c>
+      <c r="C1422" s="4" t="s">
         <v>3340</v>
       </c>
-      <c r="C1422" s="4" t="s">
+      <c r="D1422" s="4" t="s">
         <v>3341</v>
-      </c>
-      <c r="D1422" s="4" t="s">
-        <v>3342</v>
       </c>
     </row>
     <row r="1423" spans="1:6" x14ac:dyDescent="0.25">
@@ -24673,15 +24694,15 @@
         <v>199</v>
       </c>
       <c r="B1423" s="10" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="1424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1424" t="s">
+        <v>3345</v>
+      </c>
+      <c r="B1424" t="s">
         <v>3346</v>
-      </c>
-      <c r="B1424" t="s">
-        <v>3347</v>
       </c>
     </row>
     <row r="1425" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24689,15 +24710,15 @@
         <v>7</v>
       </c>
       <c r="B1425" s="12" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="1426" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1426" s="4" t="s">
+        <v>3349</v>
+      </c>
+      <c r="B1426" s="4" t="s">
         <v>3350</v>
-      </c>
-      <c r="B1426" s="4" t="s">
-        <v>3351</v>
       </c>
     </row>
     <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
@@ -24705,15 +24726,15 @@
         <v>7</v>
       </c>
       <c r="B1427" s="10" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
     </row>
     <row r="1428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1428" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B1428" t="s">
         <v>3361</v>
-      </c>
-      <c r="B1428" t="s">
-        <v>3362</v>
       </c>
     </row>
     <row r="1429" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24721,15 +24742,15 @@
         <v>7</v>
       </c>
       <c r="B1429" s="12" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="1430" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1430" s="4" t="s">
+        <v>3363</v>
+      </c>
+      <c r="B1430" s="4" t="s">
         <v>3364</v>
-      </c>
-      <c r="B1430" s="4" t="s">
-        <v>3365</v>
       </c>
     </row>
     <row r="1431" spans="1:2" x14ac:dyDescent="0.25">
@@ -24737,15 +24758,15 @@
         <v>7</v>
       </c>
       <c r="B1431" s="10" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1432" t="s">
+        <v>3366</v>
+      </c>
+      <c r="B1432" t="s">
         <v>3367</v>
-      </c>
-      <c r="B1432" t="s">
-        <v>3368</v>
       </c>
     </row>
     <row r="1433" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24753,15 +24774,15 @@
         <v>7</v>
       </c>
       <c r="B1433" s="12" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="1434" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1434" s="4" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B1434" s="4" t="s">
         <v>3370</v>
-      </c>
-      <c r="B1434" s="4" t="s">
-        <v>3371</v>
       </c>
     </row>
     <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
@@ -24769,87 +24790,87 @@
         <v>7</v>
       </c>
       <c r="B1435" s="10" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1436" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="B1436" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="1437" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1437" s="4" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="B1437" s="12" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="1438" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1438" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="B1438" s="4" t="s">
         <v>3382</v>
-      </c>
-      <c r="B1438" s="4" t="s">
-        <v>3383</v>
       </c>
     </row>
     <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1439" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="B1439" s="10" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1440" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B1440" t="s">
         <v>3386</v>
-      </c>
-      <c r="B1440" t="s">
-        <v>3387</v>
       </c>
     </row>
     <row r="1441" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1441" s="13" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="B1441" s="14" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="1442" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1442" s="13" t="s">
+        <v>3390</v>
+      </c>
+      <c r="B1442" s="13" t="s">
         <v>3391</v>
-      </c>
-      <c r="B1442" s="13" t="s">
-        <v>3392</v>
       </c>
     </row>
     <row r="1443" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1443" s="4" t="s">
+        <v>3403</v>
+      </c>
+      <c r="B1443" s="12" t="s">
         <v>3404</v>
-      </c>
-      <c r="B1443" s="12" t="s">
-        <v>3405</v>
       </c>
     </row>
     <row r="1444" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1444" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="B1444" s="4" t="s">
         <v>3406</v>
-      </c>
-      <c r="B1444" s="4" t="s">
-        <v>3407</v>
       </c>
     </row>
     <row r="1445" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1445" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B1445" s="10" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="1446" spans="1:14" x14ac:dyDescent="0.25">
@@ -24862,25 +24883,25 @@
     </row>
     <row r="1447" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1447" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="B1447" s="12" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C1447" s="12" t="s">
         <v>3248</v>
       </c>
-      <c r="C1447" s="12" t="s">
+      <c r="D1447" s="12" t="s">
         <v>3249</v>
       </c>
-      <c r="D1447" s="12" t="s">
+      <c r="E1447" s="12" t="s">
         <v>3250</v>
       </c>
-      <c r="E1447" s="12" t="s">
+      <c r="F1447" s="12" t="s">
         <v>3251</v>
       </c>
-      <c r="F1447" s="12" t="s">
+      <c r="G1447" s="12" t="s">
         <v>3252</v>
-      </c>
-      <c r="G1447" s="12" t="s">
-        <v>3253</v>
       </c>
       <c r="H1447" s="12" t="s">
         <v>1701</v>
@@ -24895,57 +24916,57 @@
         <v>1704</v>
       </c>
       <c r="L1447" s="12" t="s">
+        <v>3253</v>
+      </c>
+      <c r="M1447" s="12" t="s">
         <v>3254</v>
       </c>
-      <c r="M1447" s="12" t="s">
+      <c r="N1447" s="12" t="s">
         <v>3255</v>
-      </c>
-      <c r="N1447" s="12" t="s">
-        <v>3256</v>
       </c>
     </row>
     <row r="1448" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1448" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="B1448" s="4" t="s">
         <v>3415</v>
       </c>
-      <c r="B1448" s="4" t="s">
+      <c r="C1448" s="4" t="s">
+        <v>3415</v>
+      </c>
+      <c r="D1448" s="4" t="s">
+        <v>3415</v>
+      </c>
+      <c r="E1448" s="4" t="s">
         <v>3416</v>
       </c>
-      <c r="C1448" s="4" t="s">
+      <c r="F1448" s="4" t="s">
         <v>3416</v>
       </c>
-      <c r="D1448" s="4" t="s">
+      <c r="G1448" s="4" t="s">
         <v>3416</v>
       </c>
-      <c r="E1448" s="4" t="s">
+      <c r="H1448" s="4" t="s">
         <v>3417</v>
       </c>
-      <c r="F1448" s="4" t="s">
+      <c r="I1448" s="4" t="s">
         <v>3417</v>
       </c>
-      <c r="G1448" s="4" t="s">
+      <c r="J1448" s="4" t="s">
         <v>3417</v>
       </c>
-      <c r="H1448" s="4" t="s">
+      <c r="K1448" s="4" t="s">
+        <v>3417</v>
+      </c>
+      <c r="L1448" s="4" t="s">
         <v>3418</v>
       </c>
-      <c r="I1448" s="4" t="s">
+      <c r="M1448" s="4" t="s">
         <v>3418</v>
       </c>
-      <c r="J1448" s="4" t="s">
+      <c r="N1448" s="4" t="s">
         <v>3418</v>
-      </c>
-      <c r="K1448" s="4" t="s">
-        <v>3418</v>
-      </c>
-      <c r="L1448" s="4" t="s">
-        <v>3419</v>
-      </c>
-      <c r="M1448" s="4" t="s">
-        <v>3419</v>
-      </c>
-      <c r="N1448" s="4" t="s">
-        <v>3419</v>
       </c>
     </row>
     <row r="1449" spans="1:14" x14ac:dyDescent="0.25">
@@ -24953,15 +24974,15 @@
         <v>199</v>
       </c>
       <c r="B1449" s="10" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="1450" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
+        <v>3419</v>
+      </c>
+      <c r="B1450" t="s">
         <v>3420</v>
-      </c>
-      <c r="B1450" t="s">
-        <v>3421</v>
       </c>
     </row>
     <row r="1451" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -24969,15 +24990,15 @@
         <v>7</v>
       </c>
       <c r="B1451" s="12" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="1452" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1452" s="4" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="B1452" s="4" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="1453" spans="1:14" x14ac:dyDescent="0.25">
@@ -24985,15 +25006,15 @@
         <v>7</v>
       </c>
       <c r="B1453" s="10" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="1454" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1454" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="B1454" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="1455" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -25001,15 +25022,59 @@
         <v>7</v>
       </c>
       <c r="B1455" s="12" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="1456" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1456" s="4" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B1456" s="12" t="s">
-        <v>3434</v>
+        <v>3433</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1457" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B1457" s="10" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1458" t="s">
+        <v>2978</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1459" s="4" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B1459" s="12" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C1459" s="12" t="s">
+        <v>3447</v>
+      </c>
+      <c r="D1459" s="12" t="s">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1460" s="4" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B1460" s="4" t="s">
+        <v>3443</v>
+      </c>
+      <c r="C1460" s="4" t="s">
+        <v>3445</v>
+      </c>
+      <c r="D1460" s="4" t="s">
+        <v>3444</v>
       </c>
     </row>
   </sheetData>
